--- a/artfynd/A 64578-2023 artfynd.xlsx
+++ b/artfynd/A 64578-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64578-2023 artfynd.xlsx
+++ b/artfynd/A 64578-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17319940</v>
+        <v>200367</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,44 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>535</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skuggmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dicranodontium denudatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>(Brid.) E.Britton</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ekebacken, 200 m O om, Vg</t>
+          <t>Tomten, ca 400 m O om, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>386544.8668006249</v>
+        <v>386553</v>
       </c>
       <c r="R2" t="n">
-        <v>6408412.085206944</v>
+        <v>6408405</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-04-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-04-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-10-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>rikligt på en stubbe + flera mindre förekomster inom 10 m radie</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,15 +771,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>fuktig skog/sumpskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>murken granstubb</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Michael Johansson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Michael Johansson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -797,12 +799,7 @@
         <v>17319952</v>
       </c>
       <c r="B3" t="n">
-        <v>93372</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386537.9951810276</v>
+        <v>386538</v>
       </c>
       <c r="R3" t="n">
-        <v>6408433.605865675</v>
+        <v>6408434</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -870,19 +867,9 @@
           <t>2015-04-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-04-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,6 +893,110 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>17319940</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ekebacken, 200 m O om, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>386545</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6408412</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rångedala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2015-04-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2015-04-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Michael Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Michael Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64578-2023 artfynd.xlsx
+++ b/artfynd/A 64578-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/200367</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17319952</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,8 +1012,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17319940</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>